--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -24890,6 +24890,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -24913,6 +24913,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -24921,7 +24921,7 @@
         <v>5000</v>
       </c>
       <c r="C1068" t="n">
-        <v>1.10000002384186</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="D1068" t="n">
         <v>1.10000002384186</v>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -24936,6 +24936,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1070" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -24800,22 +24800,22 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1063" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="C1063" t="n">
         <v>1.12000000476837</v>
       </c>
       <c r="D1063" t="n">
-        <v>1.10000002384186</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="E1063" t="n">
         <v>1.12000000476837</v>
       </c>
       <c r="F1063" t="n">
-        <v>1.11500000953674</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="G1063" t="s">
         <v>7</v>
@@ -24823,22 +24823,22 @@
     </row>
     <row r="1064">
       <c r="A1064" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1064" t="n">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="C1064" t="n">
-        <v>1.125</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="D1064" t="n">
         <v>1.10000002384186</v>
       </c>
       <c r="E1064" t="n">
-        <v>1.125</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="F1064" t="n">
-        <v>1.10000002384186</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="G1064" t="s">
         <v>7</v>
@@ -24846,22 +24846,22 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1065" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="C1065" t="n">
         <v>1.125</v>
       </c>
       <c r="D1065" t="n">
-        <v>1.0900000333786</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="E1065" t="n">
-        <v>1.12000000476837</v>
+        <v>1.125</v>
       </c>
       <c r="F1065" t="n">
-        <v>1.0900000333786</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="G1065" t="s">
         <v>7</v>
@@ -24869,22 +24869,22 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1066" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="C1066" t="n">
-        <v>1.10000002384186</v>
+        <v>1.125</v>
       </c>
       <c r="D1066" t="n">
-        <v>1.07500004768372</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="E1066" t="n">
-        <v>1.08000004291534</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="F1066" t="n">
-        <v>1.08500003814697</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="G1066" t="s">
         <v>7</v>
@@ -24892,22 +24892,22 @@
     </row>
     <row r="1067">
       <c r="A1067" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1067" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C1067" t="n">
-        <v>1.10500001907349</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="D1067" t="n">
-        <v>1.07000005245209</v>
+        <v>1.07500004768372</v>
       </c>
       <c r="E1067" t="n">
-        <v>1.10500001907349</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="F1067" t="n">
-        <v>1.09500002861023</v>
+        <v>1.08500003814697</v>
       </c>
       <c r="G1067" t="s">
         <v>7</v>
@@ -24915,22 +24915,22 @@
     </row>
     <row r="1068">
       <c r="A1068" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1068" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="C1068" t="n">
         <v>1.10500001907349</v>
       </c>
       <c r="D1068" t="n">
-        <v>1.10000002384186</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="E1068" t="n">
-        <v>1.10000002384186</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="F1068" t="n">
-        <v>1.10500001907349</v>
+        <v>1.09500002861023</v>
       </c>
       <c r="G1068" t="s">
         <v>7</v>
@@ -24938,19 +24938,19 @@
     </row>
     <row r="1069">
       <c r="A1069" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1069" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C1069" t="n">
         <v>1.10500001907349</v>
       </c>
       <c r="D1069" t="n">
-        <v>1.10500001907349</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="E1069" t="n">
-        <v>1.10500001907349</v>
+        <v>1.10000002384186</v>
       </c>
       <c r="F1069" t="n">
         <v>1.10500001907349</v>
@@ -24961,24 +24961,47 @@
     </row>
     <row r="1070">
       <c r="A1070" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1070" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="C1070" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1071" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="D1071" t="n">
         <v>1.09500002861023</v>
       </c>
-      <c r="D1070" t="n">
-        <v>1.0900000333786</v>
-      </c>
-      <c r="E1070" t="n">
+      <c r="E1071" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F1071" t="n">
         <v>1.09500002861023</v>
       </c>
-      <c r="F1070" t="n">
-        <v>1.0900000333786</v>
-      </c>
-      <c r="G1070" t="s">
+      <c r="G1071" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -28273,6 +28273,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1074" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -28299,6 +28299,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1075" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="H1075" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -28325,6 +28325,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="H1076" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -28351,6 +28351,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -28429,6 +28429,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -25274,8 +25274,31 @@
       <c r="E1083" t="n">
         <v>1.07000005245209</v>
       </c>
-      <c r="F1083"/>
+      <c r="F1083" t="n">
+        <v>1.07000005245209</v>
+      </c>
       <c r="G1083" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1084"/>
+      <c r="G1084" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -25297,8 +25297,31 @@
       <c r="E1084" t="n">
         <v>1.05999994277954</v>
       </c>
-      <c r="F1084"/>
+      <c r="F1084" t="n">
+        <v>1.07500004768372</v>
+      </c>
       <c r="G1084" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1085"/>
+      <c r="G1085" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -25320,8 +25320,31 @@
       <c r="E1085" t="n">
         <v>1.07000005245209</v>
       </c>
-      <c r="F1085"/>
+      <c r="F1085" t="n">
+        <v>1.07000005245209</v>
+      </c>
       <c r="G1085" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="F1086"/>
+      <c r="G1086" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -25343,8 +25343,31 @@
       <c r="E1086" t="n">
         <v>1.06500005722046</v>
       </c>
-      <c r="F1086"/>
+      <c r="F1086" t="n">
+        <v>1.08500003814697</v>
+      </c>
       <c r="G1086" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1087"/>
+      <c r="G1087" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -25373,6 +25373,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32075,6 +32075,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1094">
+      <c r="A1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32104,6 +32104,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1095">
+      <c r="A1095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1095" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32133,6 +32133,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1096" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32162,6 +32162,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1097" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1098" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32220,6 +32220,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1099">
+      <c r="A1099" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1099" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32249,6 +32249,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1100">
+      <c r="A1100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1100" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32278,6 +32278,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1101">
+      <c r="A1101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1101" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>1.05499994754791</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ERFO.MI.xlsx
+++ b/data/ERFO.MI.xlsx
@@ -32307,6 +32307,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1102">
+      <c r="A1102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1102" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
